--- a/协作/03-任务书.xlsx
+++ b/协作/03-任务书.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H2"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -559,6 +559,48 @@
       <c r="H2" t="inlineStr">
         <is>
           <t>2026-10-18 02:20:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>切片-0004</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>把协议与模板外置到 TEAMODEL 仓库（https://github.com/CL98K/TEAMODEL.git），DCG 不再提交协议与模板</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>TEAMODEL.md;协作/模板/**;docs/TEAMODEL_draft_v1.md;协作/**</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>dcg/**;tests/**;evidence/**;bench/**;CONTRACT.md;DESIGN.md;README.md;pyproject.toml</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>是（仅推送本仓库与 TEAMODEL 仓库，不引入外部依赖）</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>移除清单 + 引用登记 + 证据 + 记录齐备</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>约 1 小时</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>2026-10-18 03:30:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/03-任务书.xlsx
+++ b/协作/03-任务书.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:H4"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -601,6 +601,48 @@
       <c r="H3" t="inlineStr">
         <is>
           <t>2026-10-18 03:30:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>切片-0005</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>README 去掉 v2 版本叙事，把「定位」改为适配场景</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>dcg/**;tests/**;evidence/**;bench/**;CONTRACT.md;DESIGN.md;pyproject.toml</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>是（仅本地）</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>README 修订 + 证据-0014 + 记录齐备</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>约 30 分钟</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:00:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/03-任务书.xlsx
+++ b/协作/03-任务书.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H4"/>
+  <dimension ref="A1:H5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -643,6 +643,48 @@
       <c r="H4" t="inlineStr">
         <is>
           <t>2026-10-18 04:00:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>切片-0006</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>README 写明：JSONata 是结构描述语言、编译成固化 Python 提效、主场景为任意数据结构转换</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>dcg/**;tests/**;evidence/**;bench/**;CONTRACT.md;DESIGN.md;pyproject.toml</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>是（仅本地）</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>README 定位修订 + 证据-0015 + 记录齐备</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>约 20 分钟</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:25:00 +08:00</t>
         </is>
       </c>
     </row>

--- a/协作/03-任务书.xlsx
+++ b/协作/03-任务书.xlsx
@@ -465,7 +465,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H5"/>
+  <dimension ref="A1:H6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
@@ -685,6 +685,48 @@
       <c r="H5" t="inlineStr">
         <is>
           <t>2026-10-18 04:25:00 +08:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>切片-0007</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>README 删除基线/修订锚点段与 §0.1–§0.3 三个子节，§0 只保留主场景</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>README.md</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>dcg/**;tests/**;evidence/**;bench/**;CONTRACT.md;DESIGN.md;pyproject.toml</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>是（仅本地）</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>README 精简 + 证据-0016 + 记录齐备</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>约 15 分钟</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2026-10-18 04:45:00 +08:00</t>
         </is>
       </c>
     </row>
